--- a/sources/bruce_step5b.xlsx
+++ b/sources/bruce_step5b.xlsx
@@ -680,6 +680,11 @@
           <t>1</t>
         </is>
       </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>9b8fd4d4-3616-48c9-9abf-dc9f662f6010</t>
+        </is>
+      </c>
       <c r="Q5" t="inlineStr">
         <is>
           <t>9b8fd4d4-3616-48c9-9abf-dc9f662f6010</t>
@@ -727,6 +732,11 @@
           <t>2</t>
         </is>
       </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>ee9855c7-2c2c-4519-b9a4-792540aae26a</t>
+        </is>
+      </c>
       <c r="Q6" t="inlineStr">
         <is>
           <t>ee9855c7-2c2c-4519-b9a4-792540aae26a</t>
@@ -772,6 +782,11 @@
       <c r="M7" t="inlineStr">
         <is>
           <t>None</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>b9d85c75-dc82-4368-83a4-ec8806a63d3b</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
@@ -5431,6 +5446,11 @@
           <t>1+2</t>
         </is>
       </c>
+      <c r="P95" t="inlineStr">
+        <is>
+          <t>2c1913ef-7e50-4413-a74d-b2910a2ebc07</t>
+        </is>
+      </c>
       <c r="Q95" t="inlineStr">
         <is>
           <t>2c1913ef-7e50-4413-a74d-b2910a2ebc07</t>
@@ -5468,6 +5488,11 @@
           <t>1</t>
         </is>
       </c>
+      <c r="P96" t="inlineStr">
+        <is>
+          <t>0b8f5015-6736-4b0d-9890-9ab4d0f90726</t>
+        </is>
+      </c>
       <c r="Q96" t="inlineStr">
         <is>
           <t>0b8f5015-6736-4b0d-9890-9ab4d0f90726</t>
@@ -5510,6 +5535,11 @@
           <t>2</t>
         </is>
       </c>
+      <c r="P97" t="inlineStr">
+        <is>
+          <t>1765f26e-c342-4b33-8701-d1a4207176f4</t>
+        </is>
+      </c>
       <c r="Q97" t="inlineStr">
         <is>
           <t>1765f26e-c342-4b33-8701-d1a4207176f4</t>
@@ -5557,6 +5587,11 @@
           <t>Use 1 to escape if the Left Knee Strike was done with 3, use 2 if the Left Knee Strike was done with 4.</t>
         </is>
       </c>
+      <c r="P98" t="inlineStr">
+        <is>
+          <t>b8fd9af3-2ecd-4885-ae0b-82af642e3380</t>
+        </is>
+      </c>
       <c r="Q98" t="inlineStr">
         <is>
           <t>b8fd9af3-2ecd-4885-ae0b-82af642e3380</t>
@@ -5597,6 +5632,11 @@
       <c r="M99" t="inlineStr">
         <is>
           <t>None</t>
+        </is>
+      </c>
+      <c r="P99" t="inlineStr">
+        <is>
+          <t>3cdc0ff6-007b-40aa-b73f-e08284f85ced</t>
         </is>
       </c>
       <c r="Q99" t="inlineStr">

--- a/sources/bruce_step5b.xlsx
+++ b/sources/bruce_step5b.xlsx
@@ -5515,6 +5515,11 @@
           <t>– 3,1+2+3</t>
         </is>
       </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>4,1+2+3</t>
+        </is>
+      </c>
       <c r="C97" t="inlineStr">
         <is>
           <t>– Left Knee Strike</t>
